--- a/Fornecedores/Fornecedores-modelo.xlsx
+++ b/Fornecedores/Fornecedores-modelo.xlsx
@@ -22,7 +22,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Cadastro!$B$1:$L$46</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Indústria'!$B$1:$M$58</definedName>
-    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Pizzaria'!$B$1:$M$48</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Pizzaria'!$B$1:$M$47</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Homologação!$B$1:$E$21</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$45</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Ocorrências!$B$1:$K$37</definedName>
@@ -233,7 +233,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="319">
   <si>
     <t xml:space="preserve">Avaliação de fornecedores — Como usar esta planilha</t>
   </si>
@@ -946,18 +946,21 @@
     <t xml:space="preserve">Transporte de produto acabado</t>
   </si>
   <si>
+    <t xml:space="preserve">Processo terceirizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manutenção de extrusoras</t>
+  </si>
+  <si>
     <t xml:space="preserve">Serviço</t>
   </si>
   <si>
-    <t xml:space="preserve">F-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mantec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manutenção de extrusoras</t>
-  </si>
-  <si>
     <t xml:space="preserve">F-11</t>
   </si>
   <si>
@@ -974,9 +977,6 @@
   </si>
   <si>
     <t xml:space="preserve">Usinagem de moldes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processo terceirizado</t>
   </si>
   <si>
     <t xml:space="preserve">Avaliação de desempenho · julho a dezembro de 2026</t>
@@ -1927,11 +1927,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="66187211"/>
-        <c:axId val="42483766"/>
+        <c:axId val="38436450"/>
+        <c:axId val="29123134"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66187211"/>
+        <c:axId val="38436450"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1963,7 +1963,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42483766"/>
+        <c:crossAx val="29123134"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1971,7 +1971,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42483766"/>
+        <c:axId val="29123134"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -2012,7 +2012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66187211"/>
+        <c:crossAx val="38436450"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="25"/>
@@ -2197,11 +2197,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="75149420"/>
-        <c:axId val="18552538"/>
+        <c:axId val="76406349"/>
+        <c:axId val="9416432"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="75149420"/>
+        <c:axId val="76406349"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2233,7 +2233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18552538"/>
+        <c:crossAx val="9416432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2241,7 +2241,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18552538"/>
+        <c:axId val="9416432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -2282,7 +2282,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75149420"/>
+        <c:crossAx val="76406349"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="25"/>
@@ -2377,9 +2377,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Exemplo 2 - Pizzaria'!$B$22:$B$28</c:f>
+              <c:f>'Exemplo 2 - Pizzaria'!$B$22:$B$27</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>P1</c:v>
                 </c:pt>
@@ -2393,12 +2393,9 @@
                   <c:v>P4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>P5</c:v>
+                  <c:v>P6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>P6</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>P7</c:v>
                 </c:pt>
               </c:strCache>
@@ -2406,10 +2403,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Exemplo 2 - Pizzaria'!$I$22:$I$28</c:f>
+              <c:f>'Exemplo 2 - Pizzaria'!$I$22:$I$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>88.2</c:v>
                 </c:pt>
@@ -2423,12 +2420,9 @@
                   <c:v>93.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>96</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>94</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>87.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -2437,11 +2431,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="35087082"/>
-        <c:axId val="88922102"/>
+        <c:axId val="46258018"/>
+        <c:axId val="44160131"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="35087082"/>
+        <c:axId val="46258018"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2473,7 +2467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88922102"/>
+        <c:crossAx val="44160131"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2481,7 +2475,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88922102"/>
+        <c:axId val="44160131"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -2522,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35087082"/>
+        <c:crossAx val="46258018"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="25"/>
@@ -2627,13 +2621,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>128520</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>27000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -2642,7 +2636,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7048440" y="9077400"/>
+        <a:off x="7048440" y="8686800"/>
         <a:ext cx="6119640" cy="1979640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -7076,7 +7070,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="37" t="n">
-        <v>46367</v>
+        <v>46398</v>
       </c>
       <c r="E5" s="37"/>
       <c r="F5" s="37"/>
@@ -7507,7 +7501,7 @@
         <v>240</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F21" s="42" t="s">
         <v>212</v>
@@ -7532,13 +7526,13 @@
     </row>
     <row r="22" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E22" s="42" t="s">
         <v>237</v>
@@ -7566,16 +7560,16 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="40" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F23" s="42" t="s">
         <v>212</v>
@@ -8030,10 +8024,10 @@
     </row>
     <row r="37" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D37" s="42" t="s">
         <v>278</v>
@@ -8068,10 +8062,10 @@
     </row>
     <row r="38" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="40" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D38" s="42" t="s">
         <v>281</v>
@@ -8287,7 +8281,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:M35"/>
+  <dimension ref="B1:M34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -8689,7 +8683,7 @@
         <v>308</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F18" s="42" t="s">
         <v>212</v>
@@ -8914,199 +8908,161 @@
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="40" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="F26" s="42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26" s="30" t="n">
-        <f aca="false">6/6</f>
+        <f aca="false">26/26</f>
         <v>1</v>
       </c>
       <c r="H26" s="30" t="n">
-        <f aca="false">6/6</f>
+        <f aca="false">26/26</f>
         <v>1</v>
       </c>
       <c r="I26" s="31" t="n">
         <f aca="false">ROUND(50*G26+30*H26+20*F26/10,1)</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J26" s="24" t="str">
         <f aca="false">IF(I26="","",IF(I26&gt;=90,"A",IF(I26&gt;=75,"B",IF(I26&gt;=60,"C","D"))))</f>
         <v>A</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>257</v>
+        <v>317</v>
       </c>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="F27" s="42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" s="30" t="n">
-        <f aca="false">26/26</f>
-        <v>1</v>
+        <f aca="false">5/6</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="H27" s="30" t="n">
-        <f aca="false">26/26</f>
+        <f aca="false">6/6</f>
         <v>1</v>
       </c>
       <c r="I27" s="31" t="n">
         <f aca="false">ROUND(50*G27+30*H27+20*F27/10,1)</f>
-        <v>94</v>
+        <v>87.7</v>
       </c>
       <c r="J27" s="24" t="str">
         <f aca="false">IF(I27="","",IF(I27&gt;=90,"A",IF(I27&gt;=75,"B",IF(I27&gt;=60,"C","D"))))</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="40" t="s">
-        <v>306</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="D28" s="42" t="s">
-        <v>276</v>
-      </c>
-      <c r="E28" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="F28" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="G28" s="30" t="n">
-        <f aca="false">5/6</f>
-        <v>0.833333333333333</v>
-      </c>
-      <c r="H28" s="30" t="n">
-        <f aca="false">6/6</f>
-        <v>1</v>
-      </c>
-      <c r="I28" s="31" t="n">
-        <f aca="false">ROUND(50*G28+30*H28+20*F28/10,1)</f>
-        <v>87.7</v>
-      </c>
-      <c r="J28" s="24" t="str">
-        <f aca="false">IF(I28="","",IF(I28&gt;=90,"A",IF(I28&gt;=75,"B",IF(I28&gt;=60,"C","D"))))</f>
-        <v>B</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="H29" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="H30" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
+      <c r="B30" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="24" t="n">
+        <f aca="false">COUNT(I22:I27)</f>
+        <v>6</v>
+      </c>
+      <c r="F30" s="24"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
-      <c r="E31" s="24" t="n">
-        <f aca="false">COUNT(I22:I28)</f>
-        <v>7</v>
+      <c r="E31" s="24" t="str">
+        <f aca="false">COUNTIF(J22:J27,"A")&amp;", "&amp;COUNTIF(J22:J27,"B")&amp;", "&amp;COUNTIF(J22:J27,"C")&amp;" e "&amp;COUNTIF(J22:J27,"D")</f>
+        <v>4, 2, 0 e 0</v>
       </c>
       <c r="F31" s="24"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
-      <c r="E32" s="24" t="str">
-        <f aca="false">COUNTIF(J22:J28,"A")&amp;", "&amp;COUNTIF(J22:J28,"B")&amp;", "&amp;COUNTIF(J22:J28,"C")&amp;" e "&amp;COUNTIF(J22:J28,"D")</f>
-        <v>5, 2, 0 e 0</v>
-      </c>
-      <c r="F32" s="24"/>
+      <c r="E32" s="31" t="n">
+        <f aca="false">AVERAGE(I22:I27)</f>
+        <v>92.9</v>
+      </c>
+      <c r="F32" s="31"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="23" t="s">
-        <v>154</v>
+        <v>282</v>
       </c>
       <c r="C33" s="23"/>
       <c r="D33" s="23"/>
-      <c r="E33" s="31" t="n">
-        <f aca="false">AVERAGE(I22:I28)</f>
-        <v>93.3428571428571</v>
-      </c>
-      <c r="F33" s="31"/>
+      <c r="E33" s="24" t="str">
+        <f aca="false">INDEX(C22:C27,MATCH(MIN(I22:I27),I22:I27,0))</f>
+        <v>Oficina Duas Rodas</v>
+      </c>
+      <c r="F33" s="24"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C34" s="23"/>
       <c r="D34" s="23"/>
-      <c r="E34" s="24" t="str">
-        <f aca="false">INDEX(C22:C28,MATCH(MIN(I22:I28),I22:I28,0))</f>
-        <v>Oficina Duas Rodas</v>
-      </c>
-      <c r="F34" s="24"/>
-    </row>
-    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="24" t="n">
+      <c r="E34" s="24" t="n">
         <f aca="false">COUNTIF(J12:J18,"Homologação vencida")+COUNTIF(J12:J18,"Documentos pendentes")+COUNTIF(J12:J18,"Falta a homologação")</f>
         <v>1</v>
       </c>
-      <c r="F35" s="24"/>
+      <c r="F34" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="41">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B4:C4"/>
@@ -9136,9 +9092,10 @@
     <mergeCell ref="K25:M25"/>
     <mergeCell ref="K26:M26"/>
     <mergeCell ref="K27:M27"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="B32:D32"/>
@@ -9147,8 +9104,6 @@
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="E35:F35"/>
   </mergeCells>
   <conditionalFormatting sqref="J12:J18">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -9167,7 +9122,7 @@
       <formula>LEN(J12)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J22:J28">
+  <conditionalFormatting sqref="J22:J27">
     <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"A"</formula>
     </cfRule>

--- a/Fornecedores/Fornecedores-modelo.xlsx
+++ b/Fornecedores/Fornecedores-modelo.xlsx
@@ -1927,11 +1927,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="38436450"/>
-        <c:axId val="29123134"/>
+        <c:axId val="69673323"/>
+        <c:axId val="21814052"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38436450"/>
+        <c:axId val="69673323"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1963,7 +1963,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29123134"/>
+        <c:crossAx val="21814052"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1971,7 +1971,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29123134"/>
+        <c:axId val="21814052"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -2012,7 +2012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38436450"/>
+        <c:crossAx val="69673323"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="25"/>
@@ -2197,11 +2197,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="76406349"/>
-        <c:axId val="9416432"/>
+        <c:axId val="16915181"/>
+        <c:axId val="96656326"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="76406349"/>
+        <c:axId val="16915181"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2233,7 +2233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9416432"/>
+        <c:crossAx val="96656326"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2241,7 +2241,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9416432"/>
+        <c:axId val="96656326"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -2282,7 +2282,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76406349"/>
+        <c:crossAx val="16915181"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="25"/>
@@ -2431,11 +2431,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="46258018"/>
-        <c:axId val="44160131"/>
+        <c:axId val="63337707"/>
+        <c:axId val="53444475"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="46258018"/>
+        <c:axId val="63337707"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2467,7 +2467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44160131"/>
+        <c:crossAx val="53444475"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2475,7 +2475,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44160131"/>
+        <c:axId val="53444475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -2516,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46258018"/>
+        <c:crossAx val="63337707"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="25"/>
